--- a/referencias_tablero.xlsx
+++ b/referencias_tablero.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B4C7911-FCC7-44C7-BF03-B9CA681D90F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{632F1641-AAFD-461D-B3AB-CBF5D836B496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9810" yWindow="0" windowWidth="9480" windowHeight="10170" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Accesorios de puerta" sheetId="1" r:id="rId1"/>
@@ -30,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -39,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="552">
   <si>
     <t>material</t>
   </si>
@@ -1689,6 +1687,12 @@
   </si>
   <si>
     <t>BorneTierra2610.jpg</t>
+  </si>
+  <si>
+    <t>LamparaLED.jpg</t>
+  </si>
+  <si>
+    <t>Microswitch.jpg</t>
   </si>
 </sst>
 </file>
@@ -1739,7 +1743,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1766,17 +1770,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
       <right/>
       <top style="thin">
         <color auto="1"/>
@@ -1791,7 +1784,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1802,24 +1795,19 @@
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2126,7 +2114,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I96"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.54296875" customWidth="1"/>
     <col min="3" max="3" width="19.7265625" customWidth="1"/>
@@ -2160,7 +2148,7 @@
       <c r="G1" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -2181,7 +2169,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>15</v>
       </c>
       <c r="I2" s="2" t="s">
@@ -2202,7 +2190,7 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I3" s="2" t="s">
@@ -2223,7 +2211,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I4" s="2" t="s">
@@ -2244,7 +2232,7 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I5" s="2" t="s">
@@ -2265,7 +2253,7 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I6" s="2" t="s">
@@ -2286,7 +2274,7 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I7" s="2" t="s">
@@ -2307,7 +2295,7 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="7" t="s">
         <v>21</v>
       </c>
       <c r="I8" s="2" t="s">
@@ -2330,7 +2318,7 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="7" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="2" t="s">
@@ -2353,7 +2341,7 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="7" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="2" t="s">
@@ -2376,7 +2364,7 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="7" t="s">
         <v>24</v>
       </c>
       <c r="I11" s="2" t="s">
@@ -2399,7 +2387,7 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I12" s="2" t="s">
@@ -2422,7 +2410,7 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="7" t="s">
         <v>26</v>
       </c>
       <c r="I13" s="2" t="s">
@@ -2447,7 +2435,7 @@
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="7" t="s">
         <v>27</v>
       </c>
       <c r="I14" s="2" t="s">
@@ -2470,7 +2458,7 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-      <c r="H15" s="8" t="s">
+      <c r="H15" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I15" s="2" t="s">
@@ -2493,7 +2481,7 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="7" t="s">
         <v>29</v>
       </c>
       <c r="I16" s="2" t="s">
@@ -2516,7 +2504,7 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="7" t="s">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="s">
@@ -2539,7 +2527,7 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="7" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="2" t="s">
@@ -2562,7 +2550,7 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
-      <c r="H19" s="8" t="s">
+      <c r="H19" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="2" t="s">
@@ -2585,7 +2573,7 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
-      <c r="H20" s="8" t="s">
+      <c r="H20" s="7" t="s">
         <v>33</v>
       </c>
       <c r="I20" s="2" t="s">
@@ -2608,7 +2596,7 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-      <c r="H21" s="8" t="s">
+      <c r="H21" s="7" t="s">
         <v>34</v>
       </c>
       <c r="I21" s="2" t="s">
@@ -2631,7 +2619,7 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
-      <c r="H22" s="8" t="s">
+      <c r="H22" s="7" t="s">
         <v>35</v>
       </c>
       <c r="I22" s="2" t="s">
@@ -2654,7 +2642,7 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="7" t="s">
         <v>36</v>
       </c>
       <c r="I23" s="2" t="s">
@@ -2677,7 +2665,7 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="7" t="s">
         <v>37</v>
       </c>
       <c r="I24" s="2" t="s">
@@ -2700,7 +2688,7 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
-      <c r="H25" s="8" t="s">
+      <c r="H25" s="7" t="s">
         <v>38</v>
       </c>
       <c r="I25" s="2" t="s">
@@ -2726,7 +2714,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="2"/>
-      <c r="H26" s="8" t="s">
+      <c r="H26" s="7" t="s">
         <v>39</v>
       </c>
       <c r="I26" s="2" t="s">
@@ -2749,7 +2737,7 @@
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
-      <c r="H27" s="8" t="s">
+      <c r="H27" s="7" t="s">
         <v>40</v>
       </c>
       <c r="I27" s="2" t="s">
@@ -2772,7 +2760,7 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
-      <c r="H28" s="8" t="s">
+      <c r="H28" s="7" t="s">
         <v>41</v>
       </c>
       <c r="I28" s="2" t="s">
@@ -2795,7 +2783,7 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
-      <c r="H29" s="8" t="s">
+      <c r="H29" s="7" t="s">
         <v>42</v>
       </c>
       <c r="I29" s="2" t="s">
@@ -2814,7 +2802,7 @@
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
-      <c r="H30" s="8" t="s">
+      <c r="H30" s="7" t="s">
         <v>43</v>
       </c>
       <c r="I30" s="2" t="s">
@@ -2847,7 +2835,7 @@
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
-      <c r="H32" s="8" t="s">
+      <c r="H32" s="7" t="s">
         <v>44</v>
       </c>
       <c r="I32" s="2" t="s">
@@ -2870,7 +2858,7 @@
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
-      <c r="H33" s="8" t="s">
+      <c r="H33" s="7" t="s">
         <v>45</v>
       </c>
       <c r="I33" s="2" t="s">
@@ -2893,7 +2881,7 @@
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
-      <c r="H34" s="8" t="s">
+      <c r="H34" s="7" t="s">
         <v>46</v>
       </c>
       <c r="I34" s="2" t="s">
@@ -2916,7 +2904,7 @@
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
-      <c r="H35" s="8" t="s">
+      <c r="H35" s="7" t="s">
         <v>47</v>
       </c>
       <c r="I35" s="2" t="s">
@@ -2939,7 +2927,7 @@
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
-      <c r="H36" s="8" t="s">
+      <c r="H36" s="7" t="s">
         <v>48</v>
       </c>
       <c r="I36" s="2" t="s">
@@ -2962,7 +2950,7 @@
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
-      <c r="H37" s="8" t="s">
+      <c r="H37" s="7" t="s">
         <v>49</v>
       </c>
       <c r="I37" s="2" t="s">
@@ -2985,7 +2973,7 @@
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
-      <c r="H38" s="8" t="s">
+      <c r="H38" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I38" s="2" t="s">
@@ -3008,7 +2996,7 @@
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
-      <c r="H39" s="8" t="s">
+      <c r="H39" s="7" t="s">
         <v>51</v>
       </c>
       <c r="I39" s="2" t="s">
@@ -3031,7 +3019,7 @@
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
-      <c r="H40" s="8" t="s">
+      <c r="H40" s="7" t="s">
         <v>52</v>
       </c>
       <c r="I40" s="2" t="s">
@@ -3054,7 +3042,7 @@
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
-      <c r="H41" s="8" t="s">
+      <c r="H41" s="7" t="s">
         <v>53</v>
       </c>
       <c r="I41" s="2" t="s">
@@ -3077,7 +3065,7 @@
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
-      <c r="H42" s="8" t="s">
+      <c r="H42" s="7" t="s">
         <v>54</v>
       </c>
       <c r="I42" s="2" t="s">
@@ -3100,7 +3088,7 @@
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
-      <c r="H43" s="8" t="s">
+      <c r="H43" s="7" t="s">
         <v>55</v>
       </c>
       <c r="I43" s="2" t="s">
@@ -3123,7 +3111,7 @@
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
-      <c r="H44" s="8" t="s">
+      <c r="H44" s="7" t="s">
         <v>56</v>
       </c>
       <c r="I44" s="2" t="s">
@@ -3146,7 +3134,7 @@
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
-      <c r="H45" s="8" t="s">
+      <c r="H45" s="7" t="s">
         <v>57</v>
       </c>
       <c r="I45" s="2" t="s">
@@ -3169,7 +3157,7 @@
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
-      <c r="H46" s="8" t="s">
+      <c r="H46" s="7" t="s">
         <v>58</v>
       </c>
       <c r="I46" s="2" t="s">
@@ -3192,7 +3180,7 @@
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
-      <c r="H47" s="8" t="s">
+      <c r="H47" s="7" t="s">
         <v>59</v>
       </c>
       <c r="I47" s="2" t="s">
@@ -3215,7 +3203,7 @@
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
-      <c r="H48" s="8" t="s">
+      <c r="H48" s="7" t="s">
         <v>60</v>
       </c>
       <c r="I48" s="2" t="s">
@@ -3238,7 +3226,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
-      <c r="H49" s="8" t="s">
+      <c r="H49" s="7" t="s">
         <v>61</v>
       </c>
       <c r="I49" s="2" t="s">
@@ -3261,7 +3249,7 @@
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
-      <c r="H50" s="8" t="s">
+      <c r="H50" s="7" t="s">
         <v>62</v>
       </c>
       <c r="I50" s="2" t="s">
@@ -3284,7 +3272,7 @@
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
-      <c r="H51" s="8" t="s">
+      <c r="H51" s="7" t="s">
         <v>63</v>
       </c>
       <c r="I51" s="2" t="s">
@@ -3307,7 +3295,7 @@
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
-      <c r="H52" s="8" t="s">
+      <c r="H52" s="7" t="s">
         <v>64</v>
       </c>
       <c r="I52" s="2" t="s">
@@ -3330,7 +3318,7 @@
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
-      <c r="H53" s="8" t="s">
+      <c r="H53" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I53" s="2" t="s">
@@ -3353,7 +3341,7 @@
       <c r="G54" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="H54" s="8" t="s">
+      <c r="H54" s="7" t="s">
         <v>66</v>
       </c>
       <c r="I54" s="2" t="s">
@@ -3376,7 +3364,7 @@
       <c r="G55" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="H55" s="8" t="s">
+      <c r="H55" s="7" t="s">
         <v>67</v>
       </c>
       <c r="I55" s="2" t="s">
@@ -3399,7 +3387,7 @@
       <c r="G56" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="H56" s="8" t="s">
+      <c r="H56" s="7" t="s">
         <v>68</v>
       </c>
       <c r="I56" s="2" t="s">
@@ -3422,7 +3410,7 @@
       <c r="G57" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="H57" s="8" t="s">
+      <c r="H57" s="7" t="s">
         <v>69</v>
       </c>
       <c r="I57" s="2" t="s">
@@ -3445,7 +3433,7 @@
       <c r="G58" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="H58" s="8" t="s">
+      <c r="H58" s="7" t="s">
         <v>70</v>
       </c>
       <c r="I58" s="2" t="s">
@@ -3468,7 +3456,7 @@
       <c r="G59" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="H59" s="8" t="s">
+      <c r="H59" s="7" t="s">
         <v>71</v>
       </c>
       <c r="I59" s="2" t="s">
@@ -3491,7 +3479,7 @@
       <c r="G60" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="H60" s="8" t="s">
+      <c r="H60" s="7" t="s">
         <v>72</v>
       </c>
       <c r="I60" s="2" t="s">
@@ -3508,7 +3496,7 @@
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
-      <c r="H61" s="8" t="s">
+      <c r="H61" s="7" t="s">
         <v>373</v>
       </c>
       <c r="I61" s="2" t="s">
@@ -3529,7 +3517,7 @@
         <v>16</v>
       </c>
       <c r="G62" s="2"/>
-      <c r="H62" s="8" t="s">
+      <c r="H62" s="7" t="s">
         <v>81</v>
       </c>
       <c r="I62" s="2" t="s">
@@ -3550,7 +3538,7 @@
         <v>25</v>
       </c>
       <c r="G63" s="2"/>
-      <c r="H63" s="8" t="s">
+      <c r="H63" s="7" t="s">
         <v>82</v>
       </c>
       <c r="I63" s="2" t="s">
@@ -3571,7 +3559,7 @@
         <v>32</v>
       </c>
       <c r="G64" s="2"/>
-      <c r="H64" s="8" t="s">
+      <c r="H64" s="7" t="s">
         <v>83</v>
       </c>
       <c r="I64" s="2" t="s">
@@ -3592,7 +3580,7 @@
         <v>63</v>
       </c>
       <c r="G65" s="2"/>
-      <c r="H65" s="8" t="s">
+      <c r="H65" s="7" t="s">
         <v>84</v>
       </c>
       <c r="I65" s="2" t="s">
@@ -3613,7 +3601,7 @@
         <v>100</v>
       </c>
       <c r="G66" s="2"/>
-      <c r="H66" s="8" t="s">
+      <c r="H66" s="7" t="s">
         <v>85</v>
       </c>
       <c r="I66" s="2" t="s">
@@ -3634,7 +3622,7 @@
         <v>125</v>
       </c>
       <c r="G67" s="2"/>
-      <c r="H67" s="8" t="s">
+      <c r="H67" s="7" t="s">
         <v>86</v>
       </c>
       <c r="I67" s="2" t="s">
@@ -3655,7 +3643,7 @@
         <v>160</v>
       </c>
       <c r="G68" s="2"/>
-      <c r="H68" s="8" t="s">
+      <c r="H68" s="7" t="s">
         <v>87</v>
       </c>
       <c r="I68" s="2" t="s">
@@ -3676,7 +3664,7 @@
         <v>250</v>
       </c>
       <c r="G69" s="2"/>
-      <c r="H69" s="8" t="s">
+      <c r="H69" s="7" t="s">
         <v>88</v>
       </c>
       <c r="I69" s="2" t="s">
@@ -3697,7 +3685,7 @@
         <v>16</v>
       </c>
       <c r="G70" s="2"/>
-      <c r="H70" s="8" t="s">
+      <c r="H70" s="7" t="s">
         <v>90</v>
       </c>
       <c r="I70" s="2" t="s">
@@ -3718,7 +3706,7 @@
         <v>25</v>
       </c>
       <c r="G71" s="2"/>
-      <c r="H71" s="8" t="s">
+      <c r="H71" s="7" t="s">
         <v>91</v>
       </c>
       <c r="I71" s="2" t="s">
@@ -3739,7 +3727,7 @@
         <v>32</v>
       </c>
       <c r="G72" s="2"/>
-      <c r="H72" s="8" t="s">
+      <c r="H72" s="7" t="s">
         <v>92</v>
       </c>
       <c r="I72" s="2" t="s">
@@ -3760,7 +3748,7 @@
         <v>63</v>
       </c>
       <c r="G73" s="2"/>
-      <c r="H73" s="8" t="s">
+      <c r="H73" s="7" t="s">
         <v>93</v>
       </c>
       <c r="I73" s="2" t="s">
@@ -3781,7 +3769,7 @@
         <v>100</v>
       </c>
       <c r="G74" s="2"/>
-      <c r="H74" s="8" t="s">
+      <c r="H74" s="7" t="s">
         <v>94</v>
       </c>
       <c r="I74" s="2" t="s">
@@ -3802,7 +3790,7 @@
         <v>125</v>
       </c>
       <c r="G75" s="2"/>
-      <c r="H75" s="8" t="s">
+      <c r="H75" s="7" t="s">
         <v>95</v>
       </c>
       <c r="I75" s="2" t="s">
@@ -3823,7 +3811,7 @@
         <v>160</v>
       </c>
       <c r="G76" s="2"/>
-      <c r="H76" s="8" t="s">
+      <c r="H76" s="7" t="s">
         <v>96</v>
       </c>
       <c r="I76" s="2" t="s">
@@ -3844,7 +3832,7 @@
         <v>250</v>
       </c>
       <c r="G77" s="2"/>
-      <c r="H77" s="8" t="s">
+      <c r="H77" s="7" t="s">
         <v>97</v>
       </c>
       <c r="I77" s="2" t="s">
@@ -3865,7 +3853,7 @@
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
-      <c r="H78" s="8" t="s">
+      <c r="H78" s="7" t="s">
         <v>99</v>
       </c>
       <c r="I78" s="2" t="s">
@@ -3886,7 +3874,7 @@
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
-      <c r="H79" s="8" t="s">
+      <c r="H79" s="7" t="s">
         <v>100</v>
       </c>
       <c r="I79" s="2" t="s">
@@ -3907,7 +3895,7 @@
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
-      <c r="H80" s="8" t="s">
+      <c r="H80" s="7" t="s">
         <v>101</v>
       </c>
       <c r="I80" s="2" t="s">
@@ -3928,7 +3916,7 @@
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
-      <c r="H81" s="8" t="s">
+      <c r="H81" s="7" t="s">
         <v>102</v>
       </c>
       <c r="I81" s="2" t="s">
@@ -3949,7 +3937,7 @@
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
-      <c r="H82" s="8" t="s">
+      <c r="H82" s="7" t="s">
         <v>103</v>
       </c>
       <c r="I82" s="2" t="s">
@@ -3970,7 +3958,7 @@
       <c r="E83" s="2"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
-      <c r="H83" s="8" t="s">
+      <c r="H83" s="7" t="s">
         <v>104</v>
       </c>
       <c r="I83" s="2" t="s">
@@ -3991,7 +3979,7 @@
       <c r="E84" s="2"/>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
-      <c r="H84" s="8" t="s">
+      <c r="H84" s="7" t="s">
         <v>105</v>
       </c>
       <c r="I84" s="2" t="s">
@@ -4012,7 +4000,7 @@
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
-      <c r="H85" s="8" t="s">
+      <c r="H85" s="7" t="s">
         <v>106</v>
       </c>
       <c r="I85" s="2" t="s">
@@ -4033,7 +4021,7 @@
       <c r="E86" s="2"/>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
-      <c r="H86" s="8" t="s">
+      <c r="H86" s="7" t="s">
         <v>107</v>
       </c>
       <c r="I86" s="2" t="s">
@@ -4054,7 +4042,7 @@
       <c r="E87" s="2"/>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
-      <c r="H87" s="8" t="s">
+      <c r="H87" s="7" t="s">
         <v>110</v>
       </c>
       <c r="I87" s="2" t="s">
@@ -4075,7 +4063,7 @@
       <c r="E88" s="2"/>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
-      <c r="H88" s="8" t="s">
+      <c r="H88" s="7" t="s">
         <v>111</v>
       </c>
       <c r="I88" s="2" t="s">
@@ -4096,7 +4084,7 @@
       <c r="E89" s="2"/>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
-      <c r="H89" s="8" t="s">
+      <c r="H89" s="7" t="s">
         <v>112</v>
       </c>
       <c r="I89" s="2" t="s">
@@ -4115,7 +4103,7 @@
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
-      <c r="H90" s="8" t="s">
+      <c r="H90" s="7" t="s">
         <v>113</v>
       </c>
       <c r="I90" s="2" t="s">
@@ -4134,7 +4122,7 @@
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
-      <c r="H91" s="8" t="s">
+      <c r="H91" s="7" t="s">
         <v>116</v>
       </c>
       <c r="I91" s="2" t="s">
@@ -4153,7 +4141,7 @@
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
-      <c r="H92" s="8" t="s">
+      <c r="H92" s="7" t="s">
         <v>121</v>
       </c>
       <c r="I92" s="2" t="s">
@@ -4172,7 +4160,7 @@
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
-      <c r="H93" s="8" t="s">
+      <c r="H93" s="7" t="s">
         <v>122</v>
       </c>
       <c r="I93" s="2" t="s">
@@ -4191,7 +4179,7 @@
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
-      <c r="H94" s="8" t="s">
+      <c r="H94" s="7" t="s">
         <v>123</v>
       </c>
       <c r="I94" s="2" t="s">
@@ -4208,7 +4196,7 @@
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
-      <c r="H95" s="8" t="s">
+      <c r="H95" s="7" t="s">
         <v>361</v>
       </c>
       <c r="I95" s="2" t="s">
@@ -4225,7 +4213,7 @@
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
-      <c r="H96" s="8" t="s">
+      <c r="H96" s="7" t="s">
         <v>123</v>
       </c>
       <c r="I96" s="2" t="s">
@@ -4242,7 +4230,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50146FE9-23B7-4BB0-8B05-611474958111}">
   <dimension ref="A1:T130"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.54296875" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
@@ -4275,7 +4263,7 @@
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>403</v>
       </c>
     </row>
@@ -6859,650 +6847,648 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08600825-91A1-4B25-A715-A8A4DD3F810E}">
   <dimension ref="A1:G35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.90625" style="13"/>
-    <col min="2" max="2" width="24.453125" style="13" customWidth="1"/>
-    <col min="3" max="3" width="10.90625" style="13"/>
-    <col min="4" max="5" width="12.54296875" style="13" customWidth="1"/>
-    <col min="6" max="6" width="15.7265625" style="13" customWidth="1"/>
-    <col min="7" max="7" width="17.54296875" style="13" customWidth="1"/>
+    <col min="2" max="2" width="24.453125" customWidth="1"/>
+    <col min="4" max="5" width="12.54296875" customWidth="1"/>
+    <col min="6" max="6" width="15.7265625" customWidth="1"/>
+    <col min="7" max="7" width="17.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="3" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="2">
         <v>2812</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="2" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="2">
         <v>2810</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11" t="s">
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="2" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="2">
         <v>248</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11" t="s">
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="2" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="2">
         <v>2810</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11" t="s">
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="2" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="2">
         <v>2812</v>
       </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11" t="s">
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="2" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="2">
         <v>2810</v>
       </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11" t="s">
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="2" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="2">
         <v>248</v>
       </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11" t="s">
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="2" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11" t="s">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="2" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11" t="s">
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="2" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11" t="s">
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="2" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="12" t="s">
+      <c r="C12" s="2"/>
+      <c r="D12" s="9" t="s">
         <v>388</v>
       </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="11" t="s">
+      <c r="E12" s="9"/>
+      <c r="F12" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="2" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="12" t="s">
+      <c r="C13" s="2"/>
+      <c r="D13" s="9" t="s">
         <v>389</v>
       </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="11" t="s">
+      <c r="E13" s="9"/>
+      <c r="F13" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="2" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="12" t="s">
+      <c r="C14" s="2"/>
+      <c r="D14" s="9" t="s">
         <v>390</v>
       </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="11" t="s">
+      <c r="E14" s="9"/>
+      <c r="F14" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="2" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="12" t="s">
+      <c r="C15" s="2"/>
+      <c r="D15" s="9" t="s">
         <v>391</v>
       </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="11" t="s">
+      <c r="E15" s="9"/>
+      <c r="F15" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="2" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="12" t="s">
+      <c r="C16" s="2"/>
+      <c r="D16" s="9" t="s">
         <v>392</v>
       </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="11" t="s">
+      <c r="E16" s="9"/>
+      <c r="F16" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="2" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="12" t="s">
+      <c r="C17" s="2"/>
+      <c r="D17" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="E17" s="12"/>
-      <c r="F17" s="11" t="s">
+      <c r="E17" s="9"/>
+      <c r="F17" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="2" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C18" s="11"/>
-      <c r="D18" s="12" t="s">
+      <c r="C18" s="2"/>
+      <c r="D18" s="9" t="s">
         <v>394</v>
       </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="11" t="s">
+      <c r="E18" s="9"/>
+      <c r="F18" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="2" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="12" t="s">
+      <c r="C19" s="2"/>
+      <c r="D19" s="9" t="s">
         <v>395</v>
       </c>
-      <c r="E19" s="12"/>
-      <c r="F19" s="11" t="s">
+      <c r="E19" s="9"/>
+      <c r="F19" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="G19" s="2" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C20" s="11"/>
-      <c r="D20" s="12" t="s">
+      <c r="C20" s="2"/>
+      <c r="D20" s="9" t="s">
         <v>396</v>
       </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="11" t="s">
+      <c r="E20" s="9"/>
+      <c r="F20" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="G20" s="11" t="s">
+      <c r="G20" s="2" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="12" t="s">
+      <c r="C21" s="2"/>
+      <c r="D21" s="9" t="s">
         <v>397</v>
       </c>
-      <c r="E21" s="12"/>
-      <c r="F21" s="11" t="s">
+      <c r="E21" s="9"/>
+      <c r="F21" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="G21" s="11" t="s">
+      <c r="G21" s="2" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C22" s="11"/>
-      <c r="D22" s="12" t="s">
+      <c r="C22" s="2"/>
+      <c r="D22" s="9" t="s">
         <v>398</v>
       </c>
-      <c r="E22" s="12"/>
-      <c r="F22" s="11" t="s">
+      <c r="E22" s="9"/>
+      <c r="F22" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="G22" s="11" t="s">
+      <c r="G22" s="2" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11">
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2">
         <v>52</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="G23" s="11" t="s">
+      <c r="G23" s="2" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11">
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2">
         <v>62</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="2" t="s">
         <v>540</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11">
+      <c r="C25" s="9"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2">
         <v>82</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="G25" s="11" t="s">
+      <c r="G25" s="2" t="s">
         <v>541</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="9" t="s">
         <v>526</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="9" t="s">
         <v>527</v>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="9">
         <v>2612</v>
       </c>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11" t="s">
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="G26" s="11" t="s">
+      <c r="G26" s="2" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="9" t="s">
         <v>526</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="9" t="s">
         <v>527</v>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="9">
         <v>2610</v>
       </c>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11" t="s">
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="G27" s="11" t="s">
+      <c r="G27" s="2" t="s">
         <v>543</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="9" t="s">
         <v>526</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="9" t="s">
         <v>527</v>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="9">
         <v>248</v>
       </c>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11" t="s">
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="G28" s="11" t="s">
+      <c r="G28" s="2" t="s">
         <v>544</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="9">
         <v>2610</v>
       </c>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11" t="s">
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="G29" s="11" t="s">
+      <c r="G29" s="2" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="9">
         <v>2612</v>
       </c>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11" t="s">
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="G30" s="11" t="s">
+      <c r="G30" s="2" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="9">
         <v>2610</v>
       </c>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11" t="s">
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="G31" s="11" t="s">
+      <c r="G31" s="2" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="9" t="s">
         <v>538</v>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="9">
         <v>2612</v>
       </c>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11" t="s">
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="G32" s="11" t="s">
+      <c r="G32" s="2" t="s">
         <v>548</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="9" t="s">
         <v>538</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="9">
         <v>2610</v>
       </c>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11" t="s">
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="G33" s="11" t="s">
+      <c r="G33" s="2" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34" s="14"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A35" s="14"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -7514,7 +7500,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FB7074F-C391-4CA9-AE09-2D002ED9E452}">
   <dimension ref="A1:F12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="28.1796875" customWidth="1"/>
     <col min="3" max="3" width="5.6328125" customWidth="1"/>
@@ -7768,50 +7754,62 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C4DEB68-A8F6-4B2F-B73E-565D10F0FFE7}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.36328125" customWidth="1"/>
     <col min="2" max="2" width="13.90625" customWidth="1"/>
+    <col min="3" max="3" width="14.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>118</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C1" s="3" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>323</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C2" s="2"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>325</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C3" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
+      <c r="C4" s="2" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="B5" s="6"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7821,7 +7819,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04EE080F-9F99-4C6C-B937-7933F75593E1}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="5.90625" customWidth="1"/>
@@ -7984,7 +7982,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4518A75B-1A60-4049-8E92-D33221FF9224}">
   <dimension ref="A1:E27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.54296875" customWidth="1"/>
     <col min="2" max="2" width="8.08984375" customWidth="1"/>
